--- a/artfynd/A 35538-2025 artfynd.xlsx
+++ b/artfynd/A 35538-2025 artfynd.xlsx
@@ -2793,7 +2793,7 @@
         <v>136189278</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136189279</v>
       </c>
       <c r="B23" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
